--- a/diffusion-tn/validation/matrix_vs_tn_time_n=6.xlsx
+++ b/diffusion-tn/validation/matrix_vs_tn_time_n=6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aditya/Desktop/UROPS/mps-fluid-dynamics/diffusion-tn/validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005832EB-557D-F549-AC3C-076B5A7CC643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9213259-41F4-BB4D-A413-13C2D22ED55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="2" xr2:uid="{BA8B55B3-01B8-7847-87BD-AB4BE398D926}"/>
   </bookViews>
